--- a/Main/AUT_EEC_results/AUT_EEC_epem_a0.10_b0.10_chibar1_Q20_LO.xlsx
+++ b/Main/AUT_EEC_results/AUT_EEC_epem_a0.10_b0.10_chibar1_Q20_LO.xlsx
@@ -455,13 +455,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.001686401512351096</v>
+        <v>0.001681907752049459</v>
       </c>
       <c r="C2" t="n">
-        <v>0.001686401512351096</v>
+        <v>0.001681907752049459</v>
       </c>
       <c r="D2" t="n">
-        <v>0.001904181189496222</v>
+        <v>0.002313761504185147</v>
       </c>
     </row>
     <row r="3">
@@ -469,13 +469,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.001602678030674871</v>
+        <v>0.001581637043041736</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001602678030674871</v>
+        <v>0.001581637043041736</v>
       </c>
       <c r="D3" t="n">
-        <v>0.001578776841627585</v>
+        <v>0.001849496157387746</v>
       </c>
     </row>
     <row r="4">
@@ -483,13 +483,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.00152692808631105</v>
+        <v>0.001494054001898297</v>
       </c>
       <c r="C4" t="n">
-        <v>0.00152692808631105</v>
+        <v>0.001494054001898297</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001245062158915407</v>
+        <v>0.001411949300442818</v>
       </c>
     </row>
     <row r="5">
@@ -497,13 +497,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.00151376228480447</v>
+        <v>0.00147951228485926</v>
       </c>
       <c r="C5" t="n">
-        <v>0.00151376228480447</v>
+        <v>0.00147951228485926</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0009895095428874138</v>
+        <v>0.001066849722603315</v>
       </c>
     </row>
     <row r="6">
@@ -511,13 +511,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.001615951277672554</v>
+        <v>0.0015891495939928</v>
       </c>
       <c r="C6" t="n">
-        <v>0.001615951277672554</v>
+        <v>0.0015891495939928</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0008514438537417588</v>
+        <v>0.000848735418760748</v>
       </c>
     </row>
     <row r="7">
@@ -525,13 +525,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.001866115134578456</v>
+        <v>0.001852805128403238</v>
       </c>
       <c r="C7" t="n">
-        <v>0.001866115134578456</v>
+        <v>0.001852805128403238</v>
       </c>
       <c r="D7" t="n">
-        <v>0.000865983145464549</v>
+        <v>0.0008479443979490121</v>
       </c>
     </row>
     <row r="8">
@@ -539,13 +539,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.002315459132504728</v>
+        <v>0.002319312954921187</v>
       </c>
       <c r="C8" t="n">
-        <v>0.002315459132504728</v>
+        <v>0.002319312954921187</v>
       </c>
       <c r="D8" t="n">
-        <v>0.001079629758030605</v>
+        <v>0.001108545569064888</v>
       </c>
     </row>
     <row r="9">
@@ -553,13 +553,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.002937300630760804</v>
+        <v>0.002958458250300126</v>
       </c>
       <c r="C9" t="n">
-        <v>0.002937300630760804</v>
+        <v>0.002958458250300126</v>
       </c>
       <c r="D9" t="n">
-        <v>0.001541703325952704</v>
+        <v>0.001649788860227004</v>
       </c>
     </row>
     <row r="10">
@@ -567,13 +567,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>0.003681599781490875</v>
+        <v>0.003714586227310077</v>
       </c>
       <c r="C10" t="n">
-        <v>0.003681599781490875</v>
+        <v>0.003714586227310077</v>
       </c>
       <c r="D10" t="n">
-        <v>0.002226265825866075</v>
+        <v>0.002447389566684221</v>
       </c>
     </row>
     <row r="11">
@@ -581,13 +581,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>0.004484508132389355</v>
+        <v>0.004518734841132361</v>
       </c>
       <c r="C11" t="n">
-        <v>0.004484508132389355</v>
+        <v>0.004518734841132361</v>
       </c>
       <c r="D11" t="n">
-        <v>0.002869739542893062</v>
+        <v>0.003175343002096616</v>
       </c>
     </row>
     <row r="12">
@@ -595,13 +595,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>0.005254419427999351</v>
+        <v>0.005279453379901431</v>
       </c>
       <c r="C12" t="n">
-        <v>0.005254419427999351</v>
+        <v>0.005279453379901431</v>
       </c>
       <c r="D12" t="n">
-        <v>0.00314219607388254</v>
+        <v>0.003461198062193746</v>
       </c>
     </row>
     <row r="13">
@@ -609,13 +609,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>0.006080712502715541</v>
+        <v>0.006095525370069665</v>
       </c>
       <c r="C13" t="n">
-        <v>0.006080712502715541</v>
+        <v>0.006095525370069665</v>
       </c>
       <c r="D13" t="n">
-        <v>0.003160525784648241</v>
+        <v>0.003476827962395706</v>
       </c>
     </row>
     <row r="14">
@@ -623,13 +623,13 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>0.007074083323561662</v>
+        <v>0.007088217216704039</v>
       </c>
       <c r="C14" t="n">
-        <v>0.007074083323561662</v>
+        <v>0.007088217216704039</v>
       </c>
       <c r="D14" t="n">
-        <v>0.003267959765427313</v>
+        <v>0.003622628399548245</v>
       </c>
     </row>
     <row r="15">
@@ -637,13 +637,13 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>0.008185837776545858</v>
+        <v>0.00821089617251277</v>
       </c>
       <c r="C15" t="n">
-        <v>0.008185837776545858</v>
+        <v>0.00821089617251277</v>
       </c>
       <c r="D15" t="n">
-        <v>0.003582182812739955</v>
+        <v>0.004014803746227188</v>
       </c>
     </row>
     <row r="16">
@@ -651,13 +651,13 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>0.009265583338561372</v>
+        <v>0.009307245154256061</v>
       </c>
       <c r="C16" t="n">
-        <v>0.009265583338561372</v>
+        <v>0.009307245154256061</v>
       </c>
       <c r="D16" t="n">
-        <v>0.00400097453339689</v>
+        <v>0.004526674965814974</v>
       </c>
     </row>
     <row r="17">
@@ -665,13 +665,13 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>0.01014933769522847</v>
+        <v>0.01020720769407889</v>
       </c>
       <c r="C17" t="n">
-        <v>0.01014933769522847</v>
+        <v>0.01020720769407889</v>
       </c>
       <c r="D17" t="n">
-        <v>0.004405640623616853</v>
+        <v>0.005018207446598962</v>
       </c>
     </row>
     <row r="18">
@@ -679,13 +679,13 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>0.01090845147677546</v>
+        <v>0.01097777629469712</v>
       </c>
       <c r="C18" t="n">
-        <v>0.01090845147677546</v>
+        <v>0.01097777629469712</v>
       </c>
       <c r="D18" t="n">
-        <v>0.004761294642555452</v>
+        <v>0.005430370698430899</v>
       </c>
     </row>
     <row r="19">
@@ -693,13 +693,13 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>0.01143864980873029</v>
+        <v>0.01151360307821982</v>
       </c>
       <c r="C19" t="n">
-        <v>0.01143864980873029</v>
+        <v>0.01151360307821982</v>
       </c>
       <c r="D19" t="n">
-        <v>0.005046581784658615</v>
+        <v>0.005737384999562624</v>
       </c>
     </row>
     <row r="20">
@@ -707,13 +707,13 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>0.01178400347719678</v>
+        <v>0.0118572890203848</v>
       </c>
       <c r="C20" t="n">
-        <v>0.01178400347719678</v>
+        <v>0.0118572890203848</v>
       </c>
       <c r="D20" t="n">
-        <v>0.005244918355446797</v>
+        <v>0.005933788335687149</v>
       </c>
     </row>
     <row r="21">
@@ -721,13 +721,13 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>0.01191548637909173</v>
+        <v>0.01198137245793619</v>
       </c>
       <c r="C21" t="n">
-        <v>0.01191548637909173</v>
+        <v>0.01198137245793619</v>
       </c>
       <c r="D21" t="n">
-        <v>0.005332830087459138</v>
+        <v>0.006018490979881421</v>
       </c>
     </row>
     <row r="22">
@@ -735,13 +735,13 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>0.01197095329851098</v>
+        <v>0.01202692272437553</v>
       </c>
       <c r="C22" t="n">
-        <v>0.01197095329851098</v>
+        <v>0.01202692272437553</v>
       </c>
       <c r="D22" t="n">
-        <v>0.005375993772187742</v>
+        <v>0.00604122340124709</v>
       </c>
     </row>
     <row r="23">
@@ -749,13 +749,13 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>0.01179944835626082</v>
+        <v>0.01184586409924495</v>
       </c>
       <c r="C23" t="n">
-        <v>0.01179944835626082</v>
+        <v>0.01184586409924495</v>
       </c>
       <c r="D23" t="n">
-        <v>0.00531523238185501</v>
+        <v>0.005950491697905689</v>
       </c>
     </row>
     <row r="24">
@@ -763,13 +763,13 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>0.01159918827257901</v>
+        <v>0.01163864087741642</v>
       </c>
       <c r="C24" t="n">
-        <v>0.01159918827257901</v>
+        <v>0.01163864087741642</v>
       </c>
       <c r="D24" t="n">
-        <v>0.005223620696829548</v>
+        <v>0.005839120030167896</v>
       </c>
     </row>
     <row r="25">
@@ -777,13 +777,13 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>0.01133156206530162</v>
+        <v>0.01136922527997511</v>
       </c>
       <c r="C25" t="n">
-        <v>0.01133156206530162</v>
+        <v>0.01136922527997511</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0051043450505911</v>
+        <v>0.005723082723648795</v>
       </c>
     </row>
     <row r="26">
@@ -791,13 +791,13 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>0.01102141755548354</v>
+        <v>0.01106056674863514</v>
       </c>
       <c r="C26" t="n">
-        <v>0.01102141755548354</v>
+        <v>0.01106056674863514</v>
       </c>
       <c r="D26" t="n">
-        <v>0.00496565343385419</v>
+        <v>0.005595544901910616</v>
       </c>
     </row>
     <row r="27">
@@ -805,13 +805,13 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>0.01074308542768607</v>
+        <v>0.01078119793548897</v>
       </c>
       <c r="C27" t="n">
-        <v>0.01074308542768607</v>
+        <v>0.01078119793548897</v>
       </c>
       <c r="D27" t="n">
-        <v>0.004820212443076512</v>
+        <v>0.005453604544637425</v>
       </c>
     </row>
     <row r="28">
@@ -819,13 +819,13 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>0.01029067920797437</v>
+        <v>0.01033261792702573</v>
       </c>
       <c r="C28" t="n">
-        <v>0.01029067920797437</v>
+        <v>0.01033261792702573</v>
       </c>
       <c r="D28" t="n">
-        <v>0.004643135771548844</v>
+        <v>0.005296435675765425</v>
       </c>
     </row>
     <row r="29">
@@ -833,13 +833,13 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>0.01000467283787358</v>
+        <v>0.01004752772971104</v>
       </c>
       <c r="C29" t="n">
-        <v>0.01000467283787358</v>
+        <v>0.01004752772971104</v>
       </c>
       <c r="D29" t="n">
-        <v>0.004528151367158326</v>
+        <v>0.005143743195432491</v>
       </c>
     </row>
     <row r="30">
@@ -847,13 +847,13 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>0.009865357749360405</v>
+        <v>0.009912886396707073</v>
       </c>
       <c r="C30" t="n">
-        <v>0.009865357749360405</v>
+        <v>0.009912886396707073</v>
       </c>
       <c r="D30" t="n">
-        <v>0.004421783525283958</v>
+        <v>0.005035732493407898</v>
       </c>
     </row>
     <row r="31">
@@ -861,13 +861,13 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>0.009672143248027117</v>
+        <v>0.009720922013096014</v>
       </c>
       <c r="C31" t="n">
-        <v>0.009672143248027117</v>
+        <v>0.009720922013096014</v>
       </c>
       <c r="D31" t="n">
-        <v>0.004347451335618738</v>
+        <v>0.004998847793112752</v>
       </c>
     </row>
   </sheetData>
